--- a/模型表现.xlsx
+++ b/模型表现.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23360" windowHeight="9300"/>
+    <workbookView windowWidth="23360" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
   <si>
     <t>模型</t>
   </si>
@@ -122,7 +122,39 @@
     <t>AMFormer</t>
   </si>
   <si>
-    <t>整体表现最佳。</t>
+    <t>12.15.ver</t>
+  </si>
+  <si>
+    <t>AMFormer（改进1）</t>
+  </si>
+  <si>
+    <r>
+      <t>1.5.ver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>改进方法: 1. 构造关键临床比值/差值特征
+2. 修复 Embedding 逻辑
+3. 先用 XGBoost在训练折上输出概率作为“软标签”</t>
+    </r>
   </si>
   <si>
     <t>混合训练（增加了工程特征）</t>
@@ -151,7 +183,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +253,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -365,7 +404,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,6 +426,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,76 +782,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -809,10 +854,10 @@
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -821,10 +866,10 @@
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -833,10 +878,10 @@
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -845,10 +890,10 @@
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -857,11 +902,17 @@
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -907,68 +958,77 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1717,7 +1777,7 @@
       <c r="D5" s="14">
         <v>0.667</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="14">
         <v>0.755</v>
       </c>
       <c r="F5" s="14">
@@ -1753,25 +1813,25 @@
       <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>0.875</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="15">
         <v>0.831</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>0.696</v>
       </c>
       <c r="E6" s="14">
         <v>0.736</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="15">
         <v>0.716</v>
       </c>
       <c r="G6" s="12">
         <v>0.28</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="8"/>
@@ -1780,33 +1840,33 @@
       <c r="L6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="18">
+      <c r="M6" s="17">
         <v>0.87</v>
       </c>
-      <c r="N6" s="18">
+      <c r="N6" s="17">
         <v>0.89</v>
       </c>
-      <c r="O6" s="18">
+      <c r="O6" s="17">
         <v>0.93</v>
       </c>
-      <c r="P6" s="18">
+      <c r="P6" s="17">
         <v>0.78</v>
       </c>
-      <c r="Q6" s="18">
+      <c r="Q6" s="17">
         <v>0.85</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="19" t="s">
+    <row r="7" ht="16.8" spans="1:18">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="21"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="18"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -1815,7 +1875,7 @@
       <c r="O7" s="8"/>
     </row>
     <row r="8" ht="84" spans="1:18">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="20" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="11">
@@ -1839,19 +1899,19 @@
       <c r="H8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" ht="51" spans="1:18">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="11">
@@ -1875,19 +1935,19 @@
       <c r="H9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" ht="51" spans="1:18">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="14">
@@ -1911,19 +1971,19 @@
       <c r="H10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" ht="51" spans="1:18">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="14">
@@ -1935,7 +1995,7 @@
       <c r="D11" s="14">
         <v>0.594</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>0.774</v>
       </c>
       <c r="F11" s="14">
@@ -1944,179 +2004,195 @@
       <c r="G11" s="12">
         <v>0.31</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
-    <row r="12" ht="16.8" spans="1:18">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:18">
+      <c r="A12" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="23"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="21"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="31">
         <v>0.8724</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="31">
         <v>0.8306</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="31">
         <v>0.6964</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="32">
         <v>0.7358</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="31">
         <v>0.7156</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="33">
         <v>0.55</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="21"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="25"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
+    <row r="14" ht="138" spans="1:18">
+      <c r="A14" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="35">
+        <v>0.876</v>
+      </c>
+      <c r="C14" s="36">
+        <v>0.8372</v>
+      </c>
+      <c r="D14" s="36">
+        <v>0.7839</v>
+      </c>
+      <c r="E14" s="36">
+        <v>0.7873</v>
+      </c>
+      <c r="F14" s="36">
+        <v>0.7253</v>
+      </c>
+      <c r="G14" s="37">
+        <v>0.41</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="21"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="36"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="36"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="36"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" ht="34" spans="1:18">
-      <c r="A18" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="23"/>
+      <c r="A18" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="21"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="25"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" ht="51" spans="1:18">
       <c r="A19" s="10" t="s">
@@ -2141,18 +2217,18 @@
         <v>0.1</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="24"/>
+        <v>35</v>
+      </c>
+      <c r="I19" s="22"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="25"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" ht="34" spans="1:18">
       <c r="A20" s="10" t="s">
@@ -2177,18 +2253,18 @@
         <v>0.59</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="43"/>
+        <v>36</v>
+      </c>
+      <c r="I20" s="46"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="25"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" ht="51" spans="1:18">
       <c r="A21" s="10" t="s">
@@ -2213,18 +2289,18 @@
         <v>0.5</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I21" s="43"/>
+        <v>37</v>
+      </c>
+      <c r="I21" s="46"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" ht="34" spans="1:18">
       <c r="A22" s="10" t="s">
@@ -2249,26 +2325,26 @@
         <v>0.13</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
+        <v>38</v>
+      </c>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="1:18">
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="46"/>
       <c r="O23" s="8"/>
     </row>
     <row r="25" spans="1:18">
